--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2022_T1_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2022_T1_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>63</t>
+    <t>57</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,40 +69,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>10.003</t>
-  </si>
-  <si>
-    <t>(8.802)</t>
-  </si>
-  <si>
-    <t>7.016</t>
-  </si>
-  <si>
-    <t>(1.007)</t>
-  </si>
-  <si>
-    <t>4.277</t>
-  </si>
-  <si>
-    <t>(1.285)</t>
-  </si>
-  <si>
-    <t>16.500</t>
-  </si>
-  <si>
-    <t>(8.815)</t>
-  </si>
-  <si>
-    <t>1.760</t>
-  </si>
-  <si>
-    <t>(0.310)</t>
-  </si>
-  <si>
-    <t>11.381</t>
-  </si>
-  <si>
-    <t>(1.440)</t>
+    <t>1.091</t>
+  </si>
+  <si>
+    <t>(0.144)</t>
+  </si>
+  <si>
+    <t>7.684</t>
+  </si>
+  <si>
+    <t>(1.076)</t>
+  </si>
+  <si>
+    <t>2.235</t>
+  </si>
+  <si>
+    <t>(0.523)</t>
+  </si>
+  <si>
+    <t>5.708</t>
+  </si>
+  <si>
+    <t>(0.792)</t>
+  </si>
+  <si>
+    <t>1.892</t>
+  </si>
+  <si>
+    <t>(0.335)</t>
+  </si>
+  <si>
+    <t>12.474</t>
+  </si>
+  <si>
+    <t>(1.517)</t>
   </si>
   <si>
     <t>0.000</t>
@@ -111,22 +111,22 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>0.459</t>
-  </si>
-  <si>
-    <t>(0.112)</t>
-  </si>
-  <si>
-    <t>51.660</t>
-  </si>
-  <si>
-    <t>(39.529)</t>
-  </si>
-  <si>
-    <t>3.647</t>
-  </si>
-  <si>
-    <t>(1.713)</t>
+    <t>0.490</t>
+  </si>
+  <si>
+    <t>(0.122)</t>
+  </si>
+  <si>
+    <t>9.428</t>
+  </si>
+  <si>
+    <t>(1.278)</t>
+  </si>
+  <si>
+    <t>2.116</t>
+  </si>
+  <si>
+    <t>(0.421)</t>
   </si>
   <si>
     <t>53</t>
@@ -192,7 +192,7 @@
     <t>(0.722)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>.n</t>
@@ -207,31 +207,31 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-8.583</t>
-  </si>
-  <si>
-    <t>1.984</t>
-  </si>
-  <si>
-    <t>-0.160</t>
-  </si>
-  <si>
-    <t>-8.999</t>
-  </si>
-  <si>
-    <t>-0.081</t>
-  </si>
-  <si>
-    <t>-0.173</t>
-  </si>
-  <si>
-    <t>-0.174</t>
-  </si>
-  <si>
-    <t>-40.766</t>
-  </si>
-  <si>
-    <t>0.755</t>
+    <t>0.329</t>
+  </si>
+  <si>
+    <t>1.316</t>
+  </si>
+  <si>
+    <t>1.882**</t>
+  </si>
+  <si>
+    <t>1.792</t>
+  </si>
+  <si>
+    <t>-0.213</t>
+  </si>
+  <si>
+    <t>-1.266</t>
+  </si>
+  <si>
+    <t>-0.205</t>
+  </si>
+  <si>
+    <t>1.465</t>
+  </si>
+  <si>
+    <t>2.286***</t>
   </si>
 </sst>
 </file>
